--- a/GATEWAY/A1#111#SOLUTIONMEDSRLXX/SOLUTIONMED_SRL/SPHERE/4.0/report_checklist.xlsx
+++ b/GATEWAY/A1#111#SOLUTIONMEDSRLXX/SOLUTIONMED_SRL/SPHERE/4.0/report_checklist.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1170" uniqueCount="487">
   <si>
     <t xml:space="preserve">COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -544,6 +544,9 @@
     <t xml:space="preserve">VALIDAZIONE_RSA_TIMEOUT</t>
   </si>
   <si>
+    <t xml:space="preserve">La richiesta di validazione del documento è fallita ( Request Timeout ). Riprovare</t>
+  </si>
+  <si>
     <t xml:space="preserve">Retry automatico, gestito manualmente dopo N fallimenti</t>
   </si>
   <si>
@@ -1162,9 +1165,6 @@
   </si>
   <si>
     <t xml:space="preserve">Campo/sezione non gestito/a in modo strutturato dall’applicativo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L’applicativo non tratta prescrizioni</t>
   </si>
   <si>
     <t xml:space="preserve">VALIDAZIONE_CDA2_RSA_CT14_KO</t>
@@ -1760,9 +1760,6 @@
   <si>
     <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori terminologici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 28" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L’applicativo non tratta ricette</t>
   </si>
   <si>
     <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT23</t>
@@ -4973,7 +4970,9 @@
       <c r="N31" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="O31" s="36"/>
+      <c r="O31" s="36" t="s">
+        <v>93</v>
+      </c>
       <c r="P31" s="36" t="s">
         <v>65</v>
       </c>
@@ -4984,7 +4983,7 @@
         <v>67</v>
       </c>
       <c r="S31" s="36" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T31" s="36"/>
       <c r="U31" s="37"/>
@@ -5004,7 +5003,7 @@
         <v>69</v>
       </c>
       <c r="D32" s="32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E32" s="33" t="s">
         <v>88</v>
@@ -5043,7 +5042,7 @@
         <v>71</v>
       </c>
       <c r="D33" s="32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E33" s="33" t="s">
         <v>88</v>
@@ -5082,7 +5081,7 @@
         <v>73</v>
       </c>
       <c r="D34" s="32" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E34" s="33" t="s">
         <v>88</v>
@@ -5121,10 +5120,10 @@
         <v>47</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E35" s="33" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F35" s="35"/>
       <c r="G35" s="35"/>
@@ -5158,10 +5157,10 @@
         <v>47</v>
       </c>
       <c r="D36" s="32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E36" s="33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F36" s="35"/>
       <c r="G36" s="35"/>
@@ -5195,10 +5194,10 @@
         <v>47</v>
       </c>
       <c r="D37" s="32" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E37" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F37" s="35"/>
       <c r="G37" s="35"/>
@@ -5232,10 +5231,10 @@
         <v>47</v>
       </c>
       <c r="D38" s="32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E38" s="33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
@@ -5269,10 +5268,10 @@
         <v>47</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F39" s="35"/>
       <c r="G39" s="35"/>
@@ -5306,10 +5305,10 @@
         <v>47</v>
       </c>
       <c r="D40" s="32" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F40" s="35"/>
       <c r="G40" s="35"/>
@@ -5343,10 +5342,10 @@
         <v>47</v>
       </c>
       <c r="D41" s="32" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E41" s="33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F41" s="35"/>
       <c r="G41" s="35"/>
@@ -5380,10 +5379,10 @@
         <v>47</v>
       </c>
       <c r="D42" s="32" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E42" s="33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F42" s="35"/>
       <c r="G42" s="35"/>
@@ -5417,10 +5416,10 @@
         <v>54</v>
       </c>
       <c r="D43" s="32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E43" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F43" s="35"/>
       <c r="G43" s="35"/>
@@ -5454,10 +5453,10 @@
         <v>54</v>
       </c>
       <c r="D44" s="32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E44" s="33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F44" s="35"/>
       <c r="G44" s="35"/>
@@ -5491,10 +5490,10 @@
         <v>54</v>
       </c>
       <c r="D45" s="32" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E45" s="33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F45" s="35"/>
       <c r="G45" s="35"/>
@@ -5528,10 +5527,10 @@
         <v>54</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E46" s="33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F46" s="35"/>
       <c r="G46" s="35"/>
@@ -5565,10 +5564,10 @@
         <v>54</v>
       </c>
       <c r="D47" s="32" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E47" s="33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F47" s="35"/>
       <c r="G47" s="35"/>
@@ -5602,10 +5601,10 @@
         <v>54</v>
       </c>
       <c r="D48" s="32" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F48" s="35"/>
       <c r="G48" s="35"/>
@@ -5639,10 +5638,10 @@
         <v>54</v>
       </c>
       <c r="D49" s="32" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E49" s="33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F49" s="35"/>
       <c r="G49" s="35"/>
@@ -5676,10 +5675,10 @@
         <v>54</v>
       </c>
       <c r="D50" s="32" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E50" s="33" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F50" s="35"/>
       <c r="G50" s="35"/>
@@ -5713,10 +5712,10 @@
         <v>54</v>
       </c>
       <c r="D51" s="32" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E51" s="33" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F51" s="35"/>
       <c r="G51" s="35"/>
@@ -5750,10 +5749,10 @@
         <v>54</v>
       </c>
       <c r="D52" s="32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E52" s="33" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F52" s="35"/>
       <c r="G52" s="35"/>
@@ -5787,10 +5786,10 @@
         <v>58</v>
       </c>
       <c r="D53" s="32" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E53" s="33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F53" s="35"/>
       <c r="G53" s="35"/>
@@ -5824,10 +5823,10 @@
         <v>58</v>
       </c>
       <c r="D54" s="32" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E54" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F54" s="35"/>
       <c r="G54" s="35"/>
@@ -5861,10 +5860,10 @@
         <v>58</v>
       </c>
       <c r="D55" s="32" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E55" s="33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F55" s="35"/>
       <c r="G55" s="35"/>
@@ -5898,10 +5897,10 @@
         <v>58</v>
       </c>
       <c r="D56" s="32" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E56" s="33" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F56" s="35"/>
       <c r="G56" s="35"/>
@@ -5935,10 +5934,10 @@
         <v>58</v>
       </c>
       <c r="D57" s="32" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E57" s="33" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F57" s="35"/>
       <c r="G57" s="35"/>
@@ -5972,10 +5971,10 @@
         <v>58</v>
       </c>
       <c r="D58" s="32" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E58" s="33" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F58" s="35"/>
       <c r="G58" s="35"/>
@@ -6009,10 +6008,10 @@
         <v>58</v>
       </c>
       <c r="D59" s="32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E59" s="33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F59" s="35"/>
       <c r="G59" s="35"/>
@@ -6046,10 +6045,10 @@
         <v>58</v>
       </c>
       <c r="D60" s="32" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E60" s="33" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F60" s="35"/>
       <c r="G60" s="35"/>
@@ -6083,10 +6082,10 @@
         <v>58</v>
       </c>
       <c r="D61" s="32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E61" s="33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F61" s="35"/>
       <c r="G61" s="35"/>
@@ -6120,10 +6119,10 @@
         <v>58</v>
       </c>
       <c r="D62" s="32" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E62" s="33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F62" s="35"/>
       <c r="G62" s="35"/>
@@ -6157,10 +6156,10 @@
         <v>58</v>
       </c>
       <c r="D63" s="32" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E63" s="33" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F63" s="35"/>
       <c r="G63" s="35"/>
@@ -6194,10 +6193,10 @@
         <v>58</v>
       </c>
       <c r="D64" s="32" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E64" s="33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F64" s="35"/>
       <c r="G64" s="35"/>
@@ -6231,10 +6230,10 @@
         <v>58</v>
       </c>
       <c r="D65" s="32" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E65" s="33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F65" s="35"/>
       <c r="G65" s="35"/>
@@ -6268,10 +6267,10 @@
         <v>58</v>
       </c>
       <c r="D66" s="32" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E66" s="33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F66" s="35"/>
       <c r="G66" s="35"/>
@@ -6305,10 +6304,10 @@
         <v>58</v>
       </c>
       <c r="D67" s="32" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E67" s="33" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F67" s="35"/>
       <c r="G67" s="35"/>
@@ -6342,10 +6341,10 @@
         <v>58</v>
       </c>
       <c r="D68" s="32" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E68" s="33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F68" s="35"/>
       <c r="G68" s="35"/>
@@ -6379,10 +6378,10 @@
         <v>69</v>
       </c>
       <c r="D69" s="32" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E69" s="33" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F69" s="35"/>
       <c r="G69" s="35"/>
@@ -6416,10 +6415,10 @@
         <v>69</v>
       </c>
       <c r="D70" s="32" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E70" s="33" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F70" s="35"/>
       <c r="G70" s="35"/>
@@ -6453,10 +6452,10 @@
         <v>69</v>
       </c>
       <c r="D71" s="32" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E71" s="33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F71" s="35"/>
       <c r="G71" s="35"/>
@@ -6490,10 +6489,10 @@
         <v>69</v>
       </c>
       <c r="D72" s="32" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E72" s="33" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F72" s="35"/>
       <c r="G72" s="35"/>
@@ -6527,10 +6526,10 @@
         <v>69</v>
       </c>
       <c r="D73" s="32" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E73" s="33" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F73" s="35"/>
       <c r="G73" s="35"/>
@@ -6564,10 +6563,10 @@
         <v>69</v>
       </c>
       <c r="D74" s="32" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E74" s="33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F74" s="35"/>
       <c r="G74" s="35"/>
@@ -6601,10 +6600,10 @@
         <v>69</v>
       </c>
       <c r="D75" s="32" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E75" s="33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F75" s="35"/>
       <c r="G75" s="35"/>
@@ -6638,10 +6637,10 @@
         <v>69</v>
       </c>
       <c r="D76" s="32" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E76" s="33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F76" s="35"/>
       <c r="G76" s="35"/>
@@ -6675,10 +6674,10 @@
         <v>69</v>
       </c>
       <c r="D77" s="32" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E77" s="33" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F77" s="35"/>
       <c r="G77" s="35"/>
@@ -6712,10 +6711,10 @@
         <v>69</v>
       </c>
       <c r="D78" s="32" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E78" s="33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F78" s="35"/>
       <c r="G78" s="35"/>
@@ -6749,10 +6748,10 @@
         <v>69</v>
       </c>
       <c r="D79" s="32" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E79" s="33" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F79" s="35"/>
       <c r="G79" s="35"/>
@@ -6786,10 +6785,10 @@
         <v>71</v>
       </c>
       <c r="D80" s="32" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E80" s="33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F80" s="35"/>
       <c r="G80" s="35"/>
@@ -6823,10 +6822,10 @@
         <v>71</v>
       </c>
       <c r="D81" s="32" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E81" s="33" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F81" s="35"/>
       <c r="G81" s="35"/>
@@ -6860,10 +6859,10 @@
         <v>71</v>
       </c>
       <c r="D82" s="32" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E82" s="33" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F82" s="35"/>
       <c r="G82" s="35"/>
@@ -6897,10 +6896,10 @@
         <v>71</v>
       </c>
       <c r="D83" s="32" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E83" s="33" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F83" s="35"/>
       <c r="G83" s="35"/>
@@ -6934,10 +6933,10 @@
         <v>71</v>
       </c>
       <c r="D84" s="32" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E84" s="33" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F84" s="35"/>
       <c r="G84" s="35"/>
@@ -6971,10 +6970,10 @@
         <v>71</v>
       </c>
       <c r="D85" s="32" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F85" s="35"/>
       <c r="G85" s="35"/>
@@ -7008,10 +7007,10 @@
         <v>71</v>
       </c>
       <c r="D86" s="32" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E86" s="33" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F86" s="35"/>
       <c r="G86" s="35"/>
@@ -7045,10 +7044,10 @@
         <v>71</v>
       </c>
       <c r="D87" s="32" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E87" s="33" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F87" s="35"/>
       <c r="G87" s="35"/>
@@ -7082,10 +7081,10 @@
         <v>71</v>
       </c>
       <c r="D88" s="32" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E88" s="33" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F88" s="35"/>
       <c r="G88" s="35"/>
@@ -7119,10 +7118,10 @@
         <v>71</v>
       </c>
       <c r="D89" s="32" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E89" s="33" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F89" s="35"/>
       <c r="G89" s="35"/>
@@ -7156,10 +7155,10 @@
         <v>71</v>
       </c>
       <c r="D90" s="32" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E90" s="33" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F90" s="35"/>
       <c r="G90" s="35"/>
@@ -7193,10 +7192,10 @@
         <v>71</v>
       </c>
       <c r="D91" s="32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E91" s="33" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F91" s="35"/>
       <c r="G91" s="35"/>
@@ -7230,10 +7229,10 @@
         <v>71</v>
       </c>
       <c r="D92" s="32" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E92" s="33" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F92" s="35"/>
       <c r="G92" s="35"/>
@@ -7267,10 +7266,10 @@
         <v>73</v>
       </c>
       <c r="D93" s="32" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E93" s="33" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F93" s="35"/>
       <c r="G93" s="35"/>
@@ -7304,10 +7303,10 @@
         <v>73</v>
       </c>
       <c r="D94" s="32" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E94" s="33" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F94" s="35"/>
       <c r="G94" s="35"/>
@@ -7341,10 +7340,10 @@
         <v>73</v>
       </c>
       <c r="D95" s="32" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E95" s="33" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F95" s="35"/>
       <c r="G95" s="35"/>
@@ -7378,10 +7377,10 @@
         <v>73</v>
       </c>
       <c r="D96" s="32" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E96" s="33" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F96" s="35"/>
       <c r="G96" s="35"/>
@@ -7415,10 +7414,10 @@
         <v>73</v>
       </c>
       <c r="D97" s="32" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E97" s="33" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F97" s="35"/>
       <c r="G97" s="35"/>
@@ -7452,10 +7451,10 @@
         <v>73</v>
       </c>
       <c r="D98" s="32" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E98" s="33" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F98" s="35"/>
       <c r="G98" s="35"/>
@@ -7489,10 +7488,10 @@
         <v>73</v>
       </c>
       <c r="D99" s="32" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E99" s="33" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F99" s="35"/>
       <c r="G99" s="35"/>
@@ -7526,10 +7525,10 @@
         <v>73</v>
       </c>
       <c r="D100" s="32" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E100" s="33" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F100" s="35"/>
       <c r="G100" s="35"/>
@@ -7563,10 +7562,10 @@
         <v>73</v>
       </c>
       <c r="D101" s="32" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E101" s="33" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F101" s="35"/>
       <c r="G101" s="35"/>
@@ -7600,10 +7599,10 @@
         <v>73</v>
       </c>
       <c r="D102" s="32" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E102" s="33" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F102" s="35"/>
       <c r="G102" s="35"/>
@@ -7637,10 +7636,10 @@
         <v>73</v>
       </c>
       <c r="D103" s="32" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E103" s="33" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F103" s="35"/>
       <c r="G103" s="35"/>
@@ -7674,10 +7673,10 @@
         <v>73</v>
       </c>
       <c r="D104" s="32" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E104" s="33" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F104" s="35"/>
       <c r="G104" s="35"/>
@@ -7711,10 +7710,10 @@
         <v>73</v>
       </c>
       <c r="D105" s="32" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E105" s="33" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F105" s="35"/>
       <c r="G105" s="35"/>
@@ -7748,10 +7747,10 @@
         <v>73</v>
       </c>
       <c r="D106" s="32" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E106" s="33" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F106" s="35"/>
       <c r="G106" s="35"/>
@@ -7785,10 +7784,10 @@
         <v>73</v>
       </c>
       <c r="D107" s="32" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E107" s="33" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F107" s="35"/>
       <c r="G107" s="35"/>
@@ -7822,10 +7821,10 @@
         <v>73</v>
       </c>
       <c r="D108" s="32" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E108" s="33" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F108" s="35"/>
       <c r="G108" s="35"/>
@@ -7859,10 +7858,10 @@
         <v>73</v>
       </c>
       <c r="D109" s="32" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E109" s="33" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F109" s="35"/>
       <c r="G109" s="35"/>
@@ -7896,10 +7895,10 @@
         <v>73</v>
       </c>
       <c r="D110" s="32" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E110" s="33" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F110" s="35"/>
       <c r="G110" s="35"/>
@@ -7933,10 +7932,10 @@
         <v>73</v>
       </c>
       <c r="D111" s="32" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E111" s="33" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F111" s="35"/>
       <c r="G111" s="35"/>
@@ -7970,10 +7969,10 @@
         <v>73</v>
       </c>
       <c r="D112" s="32" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E112" s="33" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F112" s="35"/>
       <c r="G112" s="35"/>
@@ -8007,10 +8006,10 @@
         <v>73</v>
       </c>
       <c r="D113" s="32" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E113" s="33" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F113" s="35"/>
       <c r="G113" s="35"/>
@@ -8044,10 +8043,10 @@
         <v>73</v>
       </c>
       <c r="D114" s="32" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E114" s="33" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F114" s="35"/>
       <c r="G114" s="35"/>
@@ -8081,10 +8080,10 @@
         <v>73</v>
       </c>
       <c r="D115" s="32" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E115" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F115" s="35"/>
       <c r="G115" s="35"/>
@@ -8118,10 +8117,10 @@
         <v>60</v>
       </c>
       <c r="D116" s="32" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E116" s="33" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F116" s="35"/>
       <c r="G116" s="35"/>
@@ -8131,7 +8130,7 @@
         <v>67</v>
       </c>
       <c r="K116" s="36" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L116" s="36"/>
       <c r="M116" s="36"/>
@@ -8159,10 +8158,10 @@
         <v>60</v>
       </c>
       <c r="D117" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E117" s="33" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F117" s="35"/>
       <c r="G117" s="35"/>
@@ -8172,7 +8171,7 @@
         <v>67</v>
       </c>
       <c r="K117" s="36" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L117" s="36"/>
       <c r="M117" s="36"/>
@@ -8200,10 +8199,10 @@
         <v>60</v>
       </c>
       <c r="D118" s="32" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E118" s="33" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F118" s="35"/>
       <c r="G118" s="35"/>
@@ -8213,7 +8212,7 @@
         <v>67</v>
       </c>
       <c r="K118" s="36" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L118" s="36"/>
       <c r="M118" s="36"/>
@@ -8241,10 +8240,10 @@
         <v>60</v>
       </c>
       <c r="D119" s="32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E119" s="33" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F119" s="35"/>
       <c r="G119" s="35"/>
@@ -8254,7 +8253,7 @@
         <v>67</v>
       </c>
       <c r="K119" s="36" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L119" s="36"/>
       <c r="M119" s="36"/>
@@ -8282,10 +8281,10 @@
         <v>60</v>
       </c>
       <c r="D120" s="32" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E120" s="33" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F120" s="35"/>
       <c r="G120" s="35"/>
@@ -8295,11 +8294,9 @@
         <v>67</v>
       </c>
       <c r="K120" s="36" t="s">
-        <v>270</v>
-      </c>
-      <c r="L120" s="36" t="s">
         <v>271</v>
       </c>
+      <c r="L120" s="36"/>
       <c r="M120" s="36"/>
       <c r="N120" s="36"/>
       <c r="O120" s="36"/>
@@ -8643,7 +8640,7 @@
         <v>67</v>
       </c>
       <c r="K126" s="36" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L126" s="36"/>
       <c r="M126" s="36"/>
@@ -8684,7 +8681,7 @@
         <v>67</v>
       </c>
       <c r="K127" s="36" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L127" s="36"/>
       <c r="M127" s="36"/>
@@ -8725,7 +8722,7 @@
         <v>67</v>
       </c>
       <c r="K128" s="36" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L128" s="36"/>
       <c r="M128" s="36"/>
@@ -8766,7 +8763,7 @@
         <v>67</v>
       </c>
       <c r="K129" s="36" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L129" s="36"/>
       <c r="M129" s="36"/>
@@ -10553,7 +10550,7 @@
         <v>67</v>
       </c>
       <c r="K176" s="36" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L176" s="32"/>
       <c r="M176" s="36"/>
@@ -11099,11 +11096,9 @@
         <v>67</v>
       </c>
       <c r="K190" s="36" t="s">
-        <v>270</v>
-      </c>
-      <c r="L190" s="36" t="s">
-        <v>446</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="L190" s="36"/>
       <c r="M190" s="36"/>
       <c r="N190" s="36"/>
       <c r="O190" s="36"/>
@@ -11129,10 +11124,10 @@
         <v>56</v>
       </c>
       <c r="D191" s="32" t="s">
+        <v>446</v>
+      </c>
+      <c r="E191" s="33" t="s">
         <v>447</v>
-      </c>
-      <c r="E191" s="33" t="s">
-        <v>448</v>
       </c>
       <c r="F191" s="35"/>
       <c r="G191" s="35"/>
@@ -11166,10 +11161,10 @@
         <v>56</v>
       </c>
       <c r="D192" s="32" t="s">
+        <v>448</v>
+      </c>
+      <c r="E192" s="33" t="s">
         <v>449</v>
-      </c>
-      <c r="E192" s="33" t="s">
-        <v>450</v>
       </c>
       <c r="F192" s="35"/>
       <c r="G192" s="35"/>
@@ -11203,10 +11198,10 @@
         <v>56</v>
       </c>
       <c r="D193" s="32" t="s">
+        <v>450</v>
+      </c>
+      <c r="E193" s="43" t="s">
         <v>451</v>
-      </c>
-      <c r="E193" s="43" t="s">
-        <v>452</v>
       </c>
       <c r="F193" s="35"/>
       <c r="G193" s="35"/>
@@ -15238,42 +15233,42 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -15306,22 +15301,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="44" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B1" s="21" t="s">
         <v>24</v>
       </c>
       <c r="C1" s="21" t="s">
+        <v>459</v>
+      </c>
+      <c r="D1" s="21" t="s">
         <v>460</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="F1" s="45" t="s">
         <v>461</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="G1" s="46" t="s">
         <v>462</v>
-      </c>
-      <c r="G1" s="46" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15329,13 +15324,13 @@
         <v>47</v>
       </c>
       <c r="B2" s="47" t="s">
+        <v>463</v>
+      </c>
+      <c r="C2" s="48" t="s">
         <v>464</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="D2" s="49" t="s">
         <v>465</v>
-      </c>
-      <c r="D2" s="49" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15343,13 +15338,13 @@
         <v>54</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C3" s="48" t="s">
+        <v>466</v>
+      </c>
+      <c r="D3" s="49" t="s">
         <v>467</v>
-      </c>
-      <c r="D3" s="49" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15357,13 +15352,13 @@
         <v>58</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C4" s="48" t="s">
+        <v>468</v>
+      </c>
+      <c r="D4" s="50" t="s">
         <v>469</v>
-      </c>
-      <c r="D4" s="50" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15371,13 +15366,13 @@
         <v>69</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C5" s="48" t="s">
+        <v>470</v>
+      </c>
+      <c r="D5" s="49" t="s">
         <v>471</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15385,13 +15380,13 @@
         <v>71</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C6" s="48" t="s">
+        <v>472</v>
+      </c>
+      <c r="D6" s="50" t="s">
         <v>473</v>
-      </c>
-      <c r="D6" s="50" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15399,13 +15394,13 @@
         <v>73</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C7" s="48" t="s">
+        <v>474</v>
+      </c>
+      <c r="D7" s="50" t="s">
         <v>475</v>
-      </c>
-      <c r="D7" s="50" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15413,13 +15408,13 @@
         <v>60</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C8" s="48" t="s">
+        <v>476</v>
+      </c>
+      <c r="D8" s="50" t="s">
         <v>477</v>
-      </c>
-      <c r="D8" s="50" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15427,27 +15422,27 @@
         <v>56</v>
       </c>
       <c r="B9" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C9" s="48" t="s">
+        <v>478</v>
+      </c>
+      <c r="D9" s="50" t="s">
         <v>479</v>
-      </c>
-      <c r="D9" s="50" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="47" t="s">
+        <v>480</v>
+      </c>
+      <c r="B10" s="47" t="s">
+        <v>463</v>
+      </c>
+      <c r="C10" s="51" t="s">
         <v>481</v>
       </c>
-      <c r="B10" s="47" t="s">
-        <v>464</v>
-      </c>
-      <c r="C10" s="51" t="s">
+      <c r="D10" s="49" t="s">
         <v>482</v>
-      </c>
-      <c r="D10" s="49" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15455,13 +15450,13 @@
         <v>351</v>
       </c>
       <c r="B11" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C11" s="48" t="s">
+        <v>483</v>
+      </c>
+      <c r="D11" s="50" t="s">
         <v>484</v>
-      </c>
-      <c r="D11" s="50" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16453,7 +16448,7 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="53" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B2" s="53" t="s">
         <v>65</v>
@@ -16461,7 +16456,7 @@
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="53" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B3" s="53" t="s">
         <v>67</v>
